--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92872</v>
+        <v>92857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100876</v>
+        <v>100892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92854</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92839</v>
+        <v>92840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92839</v>
+        <v>92840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92840</v>
+        <v>92843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92840</v>
+        <v>92843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92843</v>
+        <v>92845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92843</v>
+        <v>92845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92845</v>
+        <v>92849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92845</v>
+        <v>92849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92849</v>
+        <v>92850</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92850</v>
+        <v>92853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92850</v>
+        <v>92853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92853</v>
+        <v>92881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92853</v>
+        <v>92881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92881</v>
+        <v>92887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92881</v>
+        <v>92887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129369113</v>
       </c>
       <c r="B2" t="n">
-        <v>92888</v>
+        <v>92893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129368919</v>
       </c>
       <c r="B3" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129369195</v>
       </c>
       <c r="B4" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129369183</v>
       </c>
       <c r="B5" t="n">
-        <v>92888</v>
+        <v>92893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129369113</v>
+        <v>129368640</v>
       </c>
       <c r="B2" t="n">
-        <v>92893</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hammartorpberget, Hammartorpberget, Vrm</t>
+          <t>Västra Örten, Västra Örten, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419650</v>
+        <v>419774</v>
       </c>
       <c r="R2" t="n">
-        <v>6612577</v>
+        <v>6612731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129368919</v>
+        <v>129369113</v>
       </c>
       <c r="B3" t="n">
-        <v>92911</v>
+        <v>93215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419660</v>
+        <v>419650</v>
       </c>
       <c r="R3" t="n">
-        <v>6612602</v>
+        <v>6612577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129369195</v>
+        <v>129369183</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>93215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419649</v>
+        <v>419633</v>
       </c>
       <c r="R4" t="n">
-        <v>6612509</v>
+        <v>6612522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129369183</v>
+        <v>129368650</v>
       </c>
       <c r="B5" t="n">
-        <v>92893</v>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hammartorpberget, Hammartorpberget, Vrm</t>
+          <t>Västra Örten, Västra Örten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419633</v>
+        <v>419768</v>
       </c>
       <c r="R5" t="n">
-        <v>6612522</v>
+        <v>6612723</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1060,200 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129368919</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hammartorpberget, Hammartorpberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>419660</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6612602</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nedre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129369195</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hammartorpberget, Hammartorpberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>419649</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6612509</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nedre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34758-2024 artfynd.xlsx
+++ b/artfynd/A 34758-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129368640</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129369113</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129369183</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129368650</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129368919</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129369195</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>